--- a/summary_stats/chuuchuu_summary_2025_02.xlsx
+++ b/summary_stats/chuuchuu_summary_2025_02.xlsx
@@ -1454,25 +1454,25 @@
         <v>139</v>
       </c>
       <c r="N13" t="n">
-        <v>955</v>
+        <v>901</v>
       </c>
       <c r="O13" t="n">
-        <v>805</v>
+        <v>752</v>
       </c>
       <c r="P13" t="n">
-        <v>744</v>
+        <v>691</v>
       </c>
       <c r="Q13" t="n">
-        <v>582</v>
+        <v>534</v>
       </c>
       <c r="R13" t="n">
-        <v>457</v>
+        <v>417</v>
       </c>
       <c r="S13" t="n">
-        <v>241</v>
+        <v>206</v>
       </c>
       <c r="T13" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="U13" t="n">
         <v>1661</v>
@@ -1770,22 +1770,22 @@
         <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O17" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P17" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q17" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R17" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T17" t="n">
         <v>18</v>
@@ -1849,25 +1849,25 @@
         <v>497</v>
       </c>
       <c r="N18" t="n">
-        <v>1803</v>
+        <v>1666</v>
       </c>
       <c r="O18" t="n">
-        <v>1446</v>
+        <v>1318</v>
       </c>
       <c r="P18" t="n">
-        <v>1313</v>
+        <v>1188</v>
       </c>
       <c r="Q18" t="n">
-        <v>937</v>
+        <v>828</v>
       </c>
       <c r="R18" t="n">
-        <v>688</v>
+        <v>598</v>
       </c>
       <c r="S18" t="n">
-        <v>290</v>
+        <v>225</v>
       </c>
       <c r="T18" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="U18" t="n">
         <v>3674</v>
@@ -1928,25 +1928,25 @@
         <v>90</v>
       </c>
       <c r="N19" t="n">
-        <v>599</v>
+        <v>572</v>
       </c>
       <c r="O19" t="n">
-        <v>472</v>
+        <v>447</v>
       </c>
       <c r="P19" t="n">
-        <v>440</v>
+        <v>415</v>
       </c>
       <c r="Q19" t="n">
-        <v>332</v>
+        <v>311</v>
       </c>
       <c r="R19" t="n">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="S19" t="n">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="T19" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="U19" t="n">
         <v>1593</v>
@@ -2086,25 +2086,25 @@
         <v>1562</v>
       </c>
       <c r="N21" t="n">
-        <v>7076</v>
+        <v>6562</v>
       </c>
       <c r="O21" t="n">
-        <v>6004</v>
+        <v>5520</v>
       </c>
       <c r="P21" t="n">
-        <v>5588</v>
+        <v>5120</v>
       </c>
       <c r="Q21" t="n">
-        <v>4311</v>
+        <v>3892</v>
       </c>
       <c r="R21" t="n">
-        <v>3304</v>
+        <v>2930</v>
       </c>
       <c r="S21" t="n">
-        <v>1546</v>
+        <v>1305</v>
       </c>
       <c r="T21" t="n">
-        <v>431</v>
+        <v>320</v>
       </c>
       <c r="U21" t="n">
         <v>12428</v>
@@ -2165,25 +2165,25 @@
         <v>255</v>
       </c>
       <c r="N22" t="n">
-        <v>1914</v>
+        <v>1814</v>
       </c>
       <c r="O22" t="n">
-        <v>1598</v>
+        <v>1505</v>
       </c>
       <c r="P22" t="n">
-        <v>1509</v>
+        <v>1420</v>
       </c>
       <c r="Q22" t="n">
-        <v>1154</v>
+        <v>1077</v>
       </c>
       <c r="R22" t="n">
-        <v>917</v>
+        <v>847</v>
       </c>
       <c r="S22" t="n">
-        <v>433</v>
+        <v>385</v>
       </c>
       <c r="T22" t="n">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="U22" t="n">
         <v>3043</v>
@@ -2481,25 +2481,25 @@
         <v>27</v>
       </c>
       <c r="N26" t="n">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="O26" t="n">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="P26" t="n">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="Q26" t="n">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="R26" t="n">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="S26" t="n">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="T26" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="U26" t="n">
         <v>526</v>
@@ -2560,25 +2560,25 @@
         <v>22</v>
       </c>
       <c r="N27" t="n">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="O27" t="n">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="P27" t="n">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="Q27" t="n">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="R27" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="S27" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="T27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U27" t="n">
         <v>546</v>
@@ -2639,19 +2639,19 @@
         <v>11</v>
       </c>
       <c r="N28" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O28" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P28" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q28" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R28" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S28" t="n">
         <v>24</v>
@@ -3350,25 +3350,25 @@
         <v>276</v>
       </c>
       <c r="N37" t="n">
-        <v>744</v>
+        <v>669</v>
       </c>
       <c r="O37" t="n">
-        <v>734</v>
+        <v>660</v>
       </c>
       <c r="P37" t="n">
-        <v>729</v>
+        <v>655</v>
       </c>
       <c r="Q37" t="n">
-        <v>533</v>
+        <v>474</v>
       </c>
       <c r="R37" t="n">
-        <v>403</v>
+        <v>355</v>
       </c>
       <c r="S37" t="n">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="T37" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="U37" t="n">
         <v>3021</v>
@@ -3429,25 +3429,25 @@
         <v>27</v>
       </c>
       <c r="N38" t="n">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="O38" t="n">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="P38" t="n">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="Q38" t="n">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="R38" t="n">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="S38" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="T38" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="U38" t="n">
         <v>398</v>
@@ -3508,19 +3508,19 @@
         <v>2</v>
       </c>
       <c r="N39" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -4219,22 +4219,22 @@
         <v>13</v>
       </c>
       <c r="N48" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O48" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P48" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q48" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R48" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="S48" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T48" t="n">
         <v>0</v>
@@ -4377,22 +4377,22 @@
         <v>5344</v>
       </c>
       <c r="N50" t="n">
-        <v>3807</v>
+        <v>3685</v>
       </c>
       <c r="O50" t="n">
-        <v>2151</v>
+        <v>2057</v>
       </c>
       <c r="P50" t="n">
-        <v>1678</v>
+        <v>1597</v>
       </c>
       <c r="Q50" t="n">
-        <v>785</v>
+        <v>731</v>
       </c>
       <c r="R50" t="n">
-        <v>355</v>
+        <v>326</v>
       </c>
       <c r="S50" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="T50" t="n">
         <v>1</v>
@@ -4535,22 +4535,22 @@
         <v>807</v>
       </c>
       <c r="N52" t="n">
-        <v>437</v>
+        <v>390</v>
       </c>
       <c r="O52" t="n">
-        <v>278</v>
+        <v>248</v>
       </c>
       <c r="P52" t="n">
-        <v>244</v>
+        <v>214</v>
       </c>
       <c r="Q52" t="n">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="R52" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T52" t="n">
         <v>0</v>
@@ -4614,16 +4614,16 @@
         <v>16</v>
       </c>
       <c r="N53" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O53" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P53" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q53" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="R53" t="n">
         <v>83</v>
@@ -4851,7 +4851,7 @@
         <v>451</v>
       </c>
       <c r="N56" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="O56" t="n">
         <v>115</v>
@@ -5009,19 +5009,19 @@
         <v>8948</v>
       </c>
       <c r="N58" t="n">
-        <v>4575</v>
+        <v>4456</v>
       </c>
       <c r="O58" t="n">
-        <v>2108</v>
+        <v>2049</v>
       </c>
       <c r="P58" t="n">
-        <v>1534</v>
+        <v>1490</v>
       </c>
       <c r="Q58" t="n">
-        <v>608</v>
+        <v>588</v>
       </c>
       <c r="R58" t="n">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="S58" t="n">
         <v>27</v>
@@ -5088,19 +5088,19 @@
         <v>4839</v>
       </c>
       <c r="N59" t="n">
-        <v>2081</v>
+        <v>2047</v>
       </c>
       <c r="O59" t="n">
-        <v>838</v>
+        <v>820</v>
       </c>
       <c r="P59" t="n">
-        <v>553</v>
+        <v>539</v>
       </c>
       <c r="Q59" t="n">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="R59" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="S59" t="n">
         <v>6</v>
@@ -6194,25 +6194,25 @@
         <v>54</v>
       </c>
       <c r="N73" t="n">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="O73" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="P73" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="Q73" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="R73" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="S73" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U73" t="n">
         <v>1896</v>
@@ -6352,22 +6352,22 @@
         <v>31</v>
       </c>
       <c r="N75" t="n">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="O75" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="P75" t="n">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="Q75" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="R75" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="S75" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="T75" t="n">
         <v>5</v>
@@ -6431,25 +6431,25 @@
         <v>13</v>
       </c>
       <c r="N76" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O76" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P76" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q76" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="R76" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S76" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="T76" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U76" t="n">
         <v>927</v>
@@ -6826,25 +6826,25 @@
         <v>33</v>
       </c>
       <c r="N81" t="n">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="O81" t="n">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="P81" t="n">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="Q81" t="n">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="R81" t="n">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="S81" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="T81" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="U81" t="n">
         <v>1550</v>
@@ -7616,22 +7616,22 @@
         <v>6</v>
       </c>
       <c r="N91" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="O91" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="P91" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="Q91" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="R91" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="S91" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T91" t="n">
         <v>3</v>
@@ -8090,16 +8090,16 @@
         <v>203</v>
       </c>
       <c r="N97" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="O97" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="P97" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="Q97" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R97" t="n">
         <v>76</v>
@@ -9117,22 +9117,22 @@
         <v>622</v>
       </c>
       <c r="N110" t="n">
-        <v>5025</v>
+        <v>4921</v>
       </c>
       <c r="O110" t="n">
-        <v>3241</v>
+        <v>3156</v>
       </c>
       <c r="P110" t="n">
-        <v>2653</v>
+        <v>2572</v>
       </c>
       <c r="Q110" t="n">
-        <v>1358</v>
+        <v>1301</v>
       </c>
       <c r="R110" t="n">
-        <v>694</v>
+        <v>656</v>
       </c>
       <c r="S110" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="T110" t="n">
         <v>13</v>
@@ -9196,13 +9196,13 @@
         <v>55</v>
       </c>
       <c r="N111" t="n">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="O111" t="n">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="P111" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="Q111" t="n">
         <v>121</v>
@@ -9354,22 +9354,22 @@
         <v>23</v>
       </c>
       <c r="N113" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="O113" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="P113" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="Q113" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R113" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S113" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T113" t="n">
         <v>1</v>
@@ -9433,22 +9433,22 @@
         <v>164</v>
       </c>
       <c r="N114" t="n">
-        <v>2253</v>
+        <v>2246</v>
       </c>
       <c r="O114" t="n">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="P114" t="n">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="Q114" t="n">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="R114" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="S114" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T114" t="n">
         <v>1</v>
@@ -9512,22 +9512,22 @@
         <v>35</v>
       </c>
       <c r="N115" t="n">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="O115" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="P115" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="Q115" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="R115" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S115" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T115" t="n">
         <v>0</v>
@@ -9670,16 +9670,16 @@
         <v>59</v>
       </c>
       <c r="N117" t="n">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="O117" t="n">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="P117" t="n">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Q117" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="R117" t="n">
         <v>107</v>
@@ -9749,22 +9749,22 @@
         <v>1</v>
       </c>
       <c r="N118" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O118" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P118" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q118" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R118" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T118" t="n">
         <v>0</v>
@@ -9828,22 +9828,22 @@
         <v>324</v>
       </c>
       <c r="N119" t="n">
-        <v>3406</v>
+        <v>3393</v>
       </c>
       <c r="O119" t="n">
-        <v>1936</v>
+        <v>1925</v>
       </c>
       <c r="P119" t="n">
-        <v>1533</v>
+        <v>1524</v>
       </c>
       <c r="Q119" t="n">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="R119" t="n">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="S119" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="T119" t="n">
         <v>9</v>
@@ -9907,22 +9907,22 @@
         <v>116</v>
       </c>
       <c r="N120" t="n">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="O120" t="n">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="P120" t="n">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="Q120" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R120" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S120" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T120" t="n">
         <v>0</v>
@@ -10223,16 +10223,16 @@
         <v>43</v>
       </c>
       <c r="N124" t="n">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="O124" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="P124" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="Q124" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="R124" t="n">
         <v>18</v>
@@ -10302,22 +10302,22 @@
         <v>11</v>
       </c>
       <c r="N125" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="O125" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P125" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q125" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="R125" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S125" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T125" t="n">
         <v>9</v>
@@ -10460,25 +10460,25 @@
         <v>19</v>
       </c>
       <c r="N127" t="n">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="O127" t="n">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="P127" t="n">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="Q127" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="R127" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="S127" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="T127" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U127" t="n">
         <v>1414</v>
@@ -11171,25 +11171,25 @@
         <v>171</v>
       </c>
       <c r="N136" t="n">
-        <v>2723</v>
+        <v>2658</v>
       </c>
       <c r="O136" t="n">
-        <v>1556</v>
+        <v>1494</v>
       </c>
       <c r="P136" t="n">
-        <v>1556</v>
+        <v>1494</v>
       </c>
       <c r="Q136" t="n">
-        <v>1036</v>
+        <v>981</v>
       </c>
       <c r="R136" t="n">
-        <v>754</v>
+        <v>703</v>
       </c>
       <c r="S136" t="n">
-        <v>333</v>
+        <v>292</v>
       </c>
       <c r="T136" t="n">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="U136" t="n">
         <v>11241</v>
@@ -11250,25 +11250,25 @@
         <v>2</v>
       </c>
       <c r="N137" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O137" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P137" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q137" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="R137" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="S137" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T137" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U137" t="n">
         <v>798</v>
@@ -11961,13 +11961,13 @@
         <v>7</v>
       </c>
       <c r="N146" t="n">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O146" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P146" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q146" t="n">
         <v>182</v>
@@ -12435,25 +12435,25 @@
         <v>6</v>
       </c>
       <c r="N152" t="n">
-        <v>2841</v>
+        <v>2837</v>
       </c>
       <c r="O152" t="n">
-        <v>2182</v>
+        <v>2178</v>
       </c>
       <c r="P152" t="n">
-        <v>1940</v>
+        <v>1936</v>
       </c>
       <c r="Q152" t="n">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="R152" t="n">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="S152" t="n">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="T152" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="U152" t="n">
         <v>6456</v>
@@ -12514,25 +12514,25 @@
         <v>63</v>
       </c>
       <c r="N153" t="n">
-        <v>1017</v>
+        <v>1010</v>
       </c>
       <c r="O153" t="n">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="P153" t="n">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="Q153" t="n">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="R153" t="n">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="S153" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="T153" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U153" t="n">
         <v>2757</v>
@@ -12909,22 +12909,22 @@
         <v>154</v>
       </c>
       <c r="N158" t="n">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="O158" t="n">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="P158" t="n">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="Q158" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="R158" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S158" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T158" t="n">
         <v>2</v>
@@ -13304,25 +13304,25 @@
         <v>4589</v>
       </c>
       <c r="N163" t="n">
-        <v>37866</v>
+        <v>37589</v>
       </c>
       <c r="O163" t="n">
-        <v>20521</v>
+        <v>20316</v>
       </c>
       <c r="P163" t="n">
-        <v>15956</v>
+        <v>15774</v>
       </c>
       <c r="Q163" t="n">
-        <v>7745</v>
+        <v>7617</v>
       </c>
       <c r="R163" t="n">
-        <v>4293</v>
+        <v>4203</v>
       </c>
       <c r="S163" t="n">
-        <v>1292</v>
+        <v>1252</v>
       </c>
       <c r="T163" t="n">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="U163" t="n">
         <v>203802</v>
@@ -13383,16 +13383,16 @@
         <v>198</v>
       </c>
       <c r="N164" t="n">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="O164" t="n">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="P164" t="n">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Q164" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="R164" t="n">
         <v>69</v>
@@ -14955,25 +14955,25 @@
         <v>9</v>
       </c>
       <c r="N184" t="n">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="O184" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="P184" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="Q184" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="R184" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="S184" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U184" t="n">
         <v>332</v>
@@ -15402,22 +15402,22 @@
         <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="P2" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Q2" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R2" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U2" t="n">
         <v>9</v>
@@ -15906,16 +15906,16 @@
         <v>43</v>
       </c>
       <c r="O8" t="n">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="P8" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="Q8" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="R8" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S8" t="n">
         <v>18</v>
@@ -16158,25 +16158,25 @@
         <v>19</v>
       </c>
       <c r="O11" t="n">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="P11" t="n">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="Q11" t="n">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="R11" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="S11" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="T11" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V11" t="n">
         <v>1414</v>
@@ -16662,25 +16662,25 @@
         <v>171</v>
       </c>
       <c r="O17" t="n">
-        <v>2723</v>
+        <v>2658</v>
       </c>
       <c r="P17" t="n">
-        <v>1556</v>
+        <v>1494</v>
       </c>
       <c r="Q17" t="n">
-        <v>1556</v>
+        <v>1494</v>
       </c>
       <c r="R17" t="n">
-        <v>1036</v>
+        <v>981</v>
       </c>
       <c r="S17" t="n">
-        <v>754</v>
+        <v>703</v>
       </c>
       <c r="T17" t="n">
-        <v>333</v>
+        <v>292</v>
       </c>
       <c r="U17" t="n">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="V17" t="n">
         <v>11241</v>
@@ -16746,25 +16746,25 @@
         <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P18" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q18" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R18" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="S18" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="T18" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="U18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V18" t="n">
         <v>752</v>
@@ -17124,16 +17124,16 @@
         <v>14</v>
       </c>
       <c r="O3" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="P3" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Q3" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="R3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S3" t="n">
         <v>31</v>
@@ -17376,16 +17376,16 @@
         <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
@@ -17796,22 +17796,22 @@
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
         <v>1</v>
@@ -18384,25 +18384,25 @@
         <v>497</v>
       </c>
       <c r="O18" t="n">
-        <v>1801</v>
+        <v>1664</v>
       </c>
       <c r="P18" t="n">
-        <v>1444</v>
+        <v>1316</v>
       </c>
       <c r="Q18" t="n">
-        <v>1311</v>
+        <v>1186</v>
       </c>
       <c r="R18" t="n">
-        <v>937</v>
+        <v>828</v>
       </c>
       <c r="S18" t="n">
-        <v>688</v>
+        <v>598</v>
       </c>
       <c r="T18" t="n">
-        <v>290</v>
+        <v>225</v>
       </c>
       <c r="U18" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="V18" t="n">
         <v>3669</v>
@@ -18468,25 +18468,25 @@
         <v>32</v>
       </c>
       <c r="O19" t="n">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="P19" t="n">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="Q19" t="n">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="R19" t="n">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="S19" t="n">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="T19" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="U19" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="V19" t="n">
         <v>288</v>
@@ -18636,25 +18636,25 @@
         <v>1562</v>
       </c>
       <c r="O21" t="n">
-        <v>7076</v>
+        <v>6562</v>
       </c>
       <c r="P21" t="n">
-        <v>6004</v>
+        <v>5520</v>
       </c>
       <c r="Q21" t="n">
-        <v>5588</v>
+        <v>5120</v>
       </c>
       <c r="R21" t="n">
-        <v>4311</v>
+        <v>3892</v>
       </c>
       <c r="S21" t="n">
-        <v>3304</v>
+        <v>2930</v>
       </c>
       <c r="T21" t="n">
-        <v>1546</v>
+        <v>1305</v>
       </c>
       <c r="U21" t="n">
-        <v>431</v>
+        <v>320</v>
       </c>
       <c r="V21" t="n">
         <v>12428</v>
@@ -18804,22 +18804,22 @@
         <v>6</v>
       </c>
       <c r="O23" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="P23" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q23" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="R23" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="S23" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U23" t="n">
         <v>9</v>
@@ -19560,16 +19560,16 @@
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -19644,25 +19644,25 @@
         <v>26</v>
       </c>
       <c r="O33" t="n">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="P33" t="n">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="Q33" t="n">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="R33" t="n">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="S33" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="T33" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="U33" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="V33" t="n">
         <v>406</v>
@@ -19728,16 +19728,16 @@
         <v>21</v>
       </c>
       <c r="O34" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P34" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q34" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="R34" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S34" t="n">
         <v>52</v>
@@ -19896,25 +19896,25 @@
         <v>15</v>
       </c>
       <c r="O36" t="n">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="P36" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="Q36" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="R36" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="S36" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="T36" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="U36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V36" t="n">
         <v>226</v>
@@ -19980,25 +19980,25 @@
         <v>61</v>
       </c>
       <c r="O37" t="n">
-        <v>468</v>
+        <v>440</v>
       </c>
       <c r="P37" t="n">
-        <v>399</v>
+        <v>374</v>
       </c>
       <c r="Q37" t="n">
-        <v>376</v>
+        <v>353</v>
       </c>
       <c r="R37" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="S37" t="n">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="T37" t="n">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="U37" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="V37" t="n">
         <v>694</v>
@@ -20064,25 +20064,25 @@
         <v>7</v>
       </c>
       <c r="O38" t="n">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="P38" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="Q38" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="R38" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="S38" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="T38" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
         <v>299</v>
@@ -20148,25 +20148,25 @@
         <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P39" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q39" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R39" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S39" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="T39" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V39" t="n">
         <v>216</v>
@@ -20400,25 +20400,25 @@
         <v>11</v>
       </c>
       <c r="O42" t="n">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="P42" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="Q42" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="R42" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="S42" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="T42" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="U42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V42" t="n">
         <v>199</v>
@@ -20484,25 +20484,25 @@
         <v>69</v>
       </c>
       <c r="O43" t="n">
-        <v>330</v>
+        <v>293</v>
       </c>
       <c r="P43" t="n">
-        <v>287</v>
+        <v>250</v>
       </c>
       <c r="Q43" t="n">
-        <v>273</v>
+        <v>236</v>
       </c>
       <c r="R43" t="n">
-        <v>222</v>
+        <v>187</v>
       </c>
       <c r="S43" t="n">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="T43" t="n">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="U43" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="V43" t="n">
         <v>494</v>
@@ -20568,25 +20568,25 @@
         <v>22</v>
       </c>
       <c r="O44" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="P44" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="Q44" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="R44" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="S44" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="T44" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="U44" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V44" t="n">
         <v>104</v>
@@ -20820,19 +20820,19 @@
         <v>15</v>
       </c>
       <c r="O47" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="P47" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="Q47" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="R47" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="S47" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T47" t="n">
         <v>29</v>
@@ -20904,25 +20904,25 @@
         <v>113</v>
       </c>
       <c r="O48" t="n">
-        <v>644</v>
+        <v>592</v>
       </c>
       <c r="P48" t="n">
-        <v>581</v>
+        <v>532</v>
       </c>
       <c r="Q48" t="n">
-        <v>556</v>
+        <v>508</v>
       </c>
       <c r="R48" t="n">
-        <v>468</v>
+        <v>425</v>
       </c>
       <c r="S48" t="n">
-        <v>383</v>
+        <v>343</v>
       </c>
       <c r="T48" t="n">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="U48" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="V48" t="n">
         <v>1055</v>
@@ -21072,19 +21072,19 @@
         <v>33</v>
       </c>
       <c r="O50" t="n">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="P50" t="n">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="Q50" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="R50" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="S50" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T50" t="n">
         <v>21</v>
@@ -21156,22 +21156,22 @@
         <v>17</v>
       </c>
       <c r="O51" t="n">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="P51" t="n">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="Q51" t="n">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="R51" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="S51" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T51" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="U51" t="n">
         <v>5</v>
@@ -21492,25 +21492,25 @@
         <v>27</v>
       </c>
       <c r="O55" t="n">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="P55" t="n">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="Q55" t="n">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="R55" t="n">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="S55" t="n">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="T55" t="n">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="U55" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="V55" t="n">
         <v>526</v>
@@ -21576,19 +21576,19 @@
         <v>11</v>
       </c>
       <c r="O56" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P56" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q56" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="R56" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="S56" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="T56" t="n">
         <v>24</v>
@@ -21828,19 +21828,19 @@
         <v>26</v>
       </c>
       <c r="O59" t="n">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="P59" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="Q59" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="R59" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S59" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="T59" t="n">
         <v>5</v>
@@ -22542,16 +22542,16 @@
         <v>16</v>
       </c>
       <c r="O4" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P4" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q4" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="R4" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="S4" t="n">
         <v>83</v>
@@ -22794,22 +22794,22 @@
         <v>5344</v>
       </c>
       <c r="O7" t="n">
-        <v>3807</v>
+        <v>3685</v>
       </c>
       <c r="P7" t="n">
-        <v>2151</v>
+        <v>2057</v>
       </c>
       <c r="Q7" t="n">
-        <v>1678</v>
+        <v>1597</v>
       </c>
       <c r="R7" t="n">
-        <v>785</v>
+        <v>731</v>
       </c>
       <c r="S7" t="n">
-        <v>355</v>
+        <v>326</v>
       </c>
       <c r="T7" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="U7" t="n">
         <v>1</v>
@@ -22878,22 +22878,22 @@
         <v>807</v>
       </c>
       <c r="O8" t="n">
-        <v>437</v>
+        <v>390</v>
       </c>
       <c r="P8" t="n">
-        <v>278</v>
+        <v>248</v>
       </c>
       <c r="Q8" t="n">
-        <v>244</v>
+        <v>214</v>
       </c>
       <c r="R8" t="n">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="S8" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="T8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -23046,7 +23046,7 @@
         <v>451</v>
       </c>
       <c r="O10" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="P10" t="n">
         <v>115</v>
@@ -23214,19 +23214,19 @@
         <v>8948</v>
       </c>
       <c r="O12" t="n">
-        <v>4575</v>
+        <v>4456</v>
       </c>
       <c r="P12" t="n">
-        <v>2108</v>
+        <v>2049</v>
       </c>
       <c r="Q12" t="n">
-        <v>1534</v>
+        <v>1490</v>
       </c>
       <c r="R12" t="n">
-        <v>608</v>
+        <v>588</v>
       </c>
       <c r="S12" t="n">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="T12" t="n">
         <v>27</v>
@@ -23298,19 +23298,19 @@
         <v>4839</v>
       </c>
       <c r="O13" t="n">
-        <v>2081</v>
+        <v>2047</v>
       </c>
       <c r="P13" t="n">
-        <v>838</v>
+        <v>820</v>
       </c>
       <c r="Q13" t="n">
-        <v>553</v>
+        <v>539</v>
       </c>
       <c r="R13" t="n">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="S13" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="T13" t="n">
         <v>6</v>
@@ -23550,22 +23550,22 @@
         <v>13</v>
       </c>
       <c r="O16" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P16" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q16" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R16" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S16" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="T16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -27372,25 +27372,25 @@
         <v>54</v>
       </c>
       <c r="O44" t="n">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="P44" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q44" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="R44" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S44" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="T44" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V44" t="n">
         <v>1896</v>
@@ -27540,22 +27540,22 @@
         <v>31</v>
       </c>
       <c r="O46" t="n">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="P46" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="Q46" t="n">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="R46" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="S46" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="T46" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="U46" t="n">
         <v>5</v>
@@ -27624,25 +27624,25 @@
         <v>12</v>
       </c>
       <c r="O47" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P47" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q47" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R47" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="S47" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="T47" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="U47" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V47" t="n">
         <v>884</v>
@@ -29262,16 +29262,16 @@
         <v>203</v>
       </c>
       <c r="O12" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="P12" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="Q12" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="R12" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S12" t="n">
         <v>76</v>
@@ -30018,22 +30018,22 @@
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P21" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q21" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R21" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U21" t="n">
         <v>2</v>
@@ -31194,19 +31194,19 @@
         <v>3</v>
       </c>
       <c r="O35" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T35" t="n">
         <v>2</v>
@@ -31404,22 +31404,22 @@
         <v>23</v>
       </c>
       <c r="O2" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="P2" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="Q2" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="R2" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="S2" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="T2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U2" t="n">
         <v>1</v>
@@ -31740,22 +31740,22 @@
         <v>622</v>
       </c>
       <c r="O6" t="n">
-        <v>5025</v>
+        <v>4921</v>
       </c>
       <c r="P6" t="n">
-        <v>3241</v>
+        <v>3156</v>
       </c>
       <c r="Q6" t="n">
-        <v>2653</v>
+        <v>2572</v>
       </c>
       <c r="R6" t="n">
-        <v>1358</v>
+        <v>1301</v>
       </c>
       <c r="S6" t="n">
-        <v>694</v>
+        <v>656</v>
       </c>
       <c r="T6" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="U6" t="n">
         <v>13</v>
@@ -31824,13 +31824,13 @@
         <v>55</v>
       </c>
       <c r="O7" t="n">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="P7" t="n">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="Q7" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="R7" t="n">
         <v>121</v>
@@ -31992,22 +31992,22 @@
         <v>164</v>
       </c>
       <c r="O9" t="n">
-        <v>2253</v>
+        <v>2246</v>
       </c>
       <c r="P9" t="n">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="Q9" t="n">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="R9" t="n">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="S9" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="T9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U9" t="n">
         <v>1</v>
@@ -32076,22 +32076,22 @@
         <v>35</v>
       </c>
       <c r="O10" t="n">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P10" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="Q10" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R10" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="S10" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="T10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -32160,16 +32160,16 @@
         <v>59</v>
       </c>
       <c r="O11" t="n">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="P11" t="n">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="Q11" t="n">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="R11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="S11" t="n">
         <v>107</v>
@@ -32244,22 +32244,22 @@
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -32328,22 +32328,22 @@
         <v>324</v>
       </c>
       <c r="O13" t="n">
-        <v>3406</v>
+        <v>3393</v>
       </c>
       <c r="P13" t="n">
-        <v>1936</v>
+        <v>1925</v>
       </c>
       <c r="Q13" t="n">
-        <v>1533</v>
+        <v>1524</v>
       </c>
       <c r="R13" t="n">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="S13" t="n">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="T13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="U13" t="n">
         <v>9</v>
@@ -32412,22 +32412,22 @@
         <v>116</v>
       </c>
       <c r="O14" t="n">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="P14" t="n">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="Q14" t="n">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="R14" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -33966,13 +33966,13 @@
         <v>5</v>
       </c>
       <c r="O15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
         <v>3</v>
@@ -34806,25 +34806,25 @@
         <v>6</v>
       </c>
       <c r="O25" t="n">
-        <v>2841</v>
+        <v>2837</v>
       </c>
       <c r="P25" t="n">
-        <v>2182</v>
+        <v>2178</v>
       </c>
       <c r="Q25" t="n">
-        <v>1940</v>
+        <v>1936</v>
       </c>
       <c r="R25" t="n">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="S25" t="n">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="T25" t="n">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="U25" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="V25" t="n">
         <v>6456</v>
@@ -34890,25 +34890,25 @@
         <v>63</v>
       </c>
       <c r="O26" t="n">
-        <v>1017</v>
+        <v>1010</v>
       </c>
       <c r="P26" t="n">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="Q26" t="n">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="R26" t="n">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="S26" t="n">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="T26" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="U26" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V26" t="n">
         <v>2757</v>
@@ -35142,22 +35142,22 @@
         <v>154</v>
       </c>
       <c r="O29" t="n">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="P29" t="n">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="Q29" t="n">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="R29" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="S29" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U29" t="n">
         <v>2</v>
@@ -35394,25 +35394,25 @@
         <v>4589</v>
       </c>
       <c r="O32" t="n">
-        <v>37866</v>
+        <v>37589</v>
       </c>
       <c r="P32" t="n">
-        <v>20521</v>
+        <v>20316</v>
       </c>
       <c r="Q32" t="n">
-        <v>15956</v>
+        <v>15774</v>
       </c>
       <c r="R32" t="n">
-        <v>7745</v>
+        <v>7617</v>
       </c>
       <c r="S32" t="n">
-        <v>4293</v>
+        <v>4203</v>
       </c>
       <c r="T32" t="n">
-        <v>1292</v>
+        <v>1252</v>
       </c>
       <c r="U32" t="n">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="V32" t="n">
         <v>203802</v>
@@ -35478,16 +35478,16 @@
         <v>198</v>
       </c>
       <c r="O33" t="n">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="P33" t="n">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="Q33" t="n">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="R33" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="S33" t="n">
         <v>69</v>
